--- a/examples/input/models/ModelB_discrete_biorecipe.xlsx
+++ b/examples/input/models/ModelB_discrete_biorecipe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10811"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasmine/Desktop/github_local_copy/VIOLIN/examples/input/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124921EF-2830-274A-B69E-8780F222EF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D202DA-EE25-6442-B401-CB408FC9C49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="1480" windowWidth="30980" windowHeight="19120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13820" yWindow="500" windowWidth="36160" windowHeight="19120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="215">
   <si>
     <t>TCR</t>
   </si>
@@ -354,9 +354,6 @@
     <t>Chemical</t>
   </si>
   <si>
-    <t>Complex</t>
-  </si>
-  <si>
     <t>Protein family</t>
   </si>
   <si>
@@ -474,9 +471,6 @@
     <t>GO:0005576</t>
   </si>
   <si>
-    <t>MTORC1_complex_nan_nan</t>
-  </si>
-  <si>
     <t>D,D</t>
   </si>
   <si>
@@ -501,24 +495,12 @@
     <t>I</t>
   </si>
   <si>
-    <t>MTORC1_complex_nan_nan,MTORC2_complex_nan_nan</t>
-  </si>
-  <si>
-    <t>PDK1_pn_nan_nan,MTORC2_complex_nan_nan</t>
-  </si>
-  <si>
     <t>AKT_pn_nan_nan</t>
   </si>
   <si>
     <t>FOS_pn_nan_nan,JUN_pn_nan_nan</t>
   </si>
   <si>
-    <t>TCR_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>FOXP3_pn_nan_nan,AP1_pn_nan_nan,NFAT_pf_nan_nan,NFKAPPAB_pn_nan_nan,STAT5_pn_nan_nan</t>
-  </si>
-  <si>
     <t>MEK2_pn_nan_nan</t>
   </si>
   <si>
@@ -531,82 +513,166 @@
     <t>CD25_pn_nan_nan,CD122_pn_nan_nan,CD132_pn_nan_nan</t>
   </si>
   <si>
-    <t>IL2R_pn_nan_nan,IL2_pn_nan_go0005576</t>
-  </si>
-  <si>
     <t>MKK7_pn_nan_nan</t>
   </si>
   <si>
-    <t>JNK_pn_nan_nan</t>
+    <t>TAK1_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>PKCTHETA_pn_nan_nan,AKT_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>PI3K_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>S6K1_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>PTEN_pn_nan_nan,FOXP3_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>TGFBETA_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>JAK3_pn_nan_nan,STAT5_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>PKCTHETA_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>CA_che_nan_nan</t>
+  </si>
+  <si>
+    <t>PIP3_che_nan_nan</t>
+  </si>
+  <si>
+    <t>FOXP3_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>PTEN_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>D,D,D,D</t>
+  </si>
+  <si>
+    <t>IL2_pn_nan_nan,IL2_pn_nan_GO0005576</t>
+  </si>
+  <si>
+    <t>UniProt</t>
+  </si>
+  <si>
+    <t>CHEBI</t>
+  </si>
+  <si>
+    <t>HMDB</t>
+  </si>
+  <si>
+    <t>Q04759</t>
+  </si>
+  <si>
+    <t>AKT1</t>
+  </si>
+  <si>
+    <t>IL2RB</t>
+  </si>
+  <si>
+    <t>IL2RG</t>
+  </si>
+  <si>
+    <t>IL2RA</t>
+  </si>
+  <si>
+    <t>EPHB2</t>
+  </si>
+  <si>
+    <t>MAP2K2</t>
+  </si>
+  <si>
+    <t>MAP2K7</t>
+  </si>
+  <si>
+    <t>PRKCQ</t>
+  </si>
+  <si>
+    <t>RPS6</t>
+  </si>
+  <si>
+    <t>RAF1</t>
+  </si>
+  <si>
+    <t>RPS6KA1</t>
+  </si>
+  <si>
+    <t>STAT5A</t>
+  </si>
+  <si>
+    <t>MAP3K7</t>
+  </si>
+  <si>
+    <t>TGFB1</t>
+  </si>
+  <si>
+    <t>Protein complex</t>
+  </si>
+  <si>
+    <t>PDK1_pn_nan_nan,MTORC2_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>TCR_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>IL2R_pf_nan_nan,IL2_pn_nan_GO0005576</t>
+  </si>
+  <si>
+    <t>JNK_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>MTORC1_pf_nan_nan,MTORC2_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>RHEB_pn_nan_nan,MTORC1_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>PI3K_pn_nan_nan,MTORC2_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>TCR_pf_nan_nan,CD28_pn_nan_nan,PI3K_pn_nan_nan,IL2_pn_nan_GO0005576,IL2R_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>TCR_pf_nan_nan,CD28_pn_nan_nan,MTORC2_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>RAS_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>TCR_pf_nan_nan,CD28_pn_nan_nan,RAS_pf_nan_nan,IL2_pn_nan_GO0005576,IL2R_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>MTORC1_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>TSC_pf_nan_nan</t>
+  </si>
+  <si>
+    <t>AP1_pf_nan_nan,NFAT_pf_nan_nan,NFKAPPAB_pf_nan_nan,IL2_pn_nan_nan</t>
+  </si>
+  <si>
+    <t>FOXP3_pn_nan_nan,AP1_pf_nan_nan,NFAT_pf_nan_nan,NFKAPPAB_pf_nan_nan,STAT5_pn_nan_nan</t>
   </si>
   <si>
     <t>RAF_pn_nan_nan</t>
   </si>
   <si>
-    <t>TAK1_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>RHEB_pn_nan_nan,MTORC1_complex_nan_nan</t>
-  </si>
-  <si>
-    <t>PI3K_pn_nan_nan,MTORC2_complex_nan_nan</t>
-  </si>
-  <si>
-    <t>PKCTHETA_pn_nan_nan,AKT_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>TCR_pn_nan_nan,CD28_pn_nan_nan,PI3K_pn_nan_nan,IL2_pn_nan_go0005576,IL2R_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>PI3K_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>TCR_pn_nan_nan,CD28_pn_nan_nan,MTORC2_complex_nan_nan</t>
-  </si>
-  <si>
-    <t>S6K1_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>PTEN_pn_nan_nan,FOXP3_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>RAS_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>TCR_pn_nan_nan,CD28_pn_nan_nan,RAS_pn_nan_nan,IL2_pn_nan_go0005576,IL2R_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>TGFBETA_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>JAK3_pn_nan_nan,STAT5_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>PKCTHETA_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>CA_che_nan_nan</t>
-  </si>
-  <si>
-    <t>PIP3_che_nan_nan</t>
-  </si>
-  <si>
-    <t>FOXP3_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>PTEN_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>TSC_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>AP1_pn_nan_nan,NFAT_pf_nan_nan,NFKAPPAB_pn_nan_nan,IL2_pn_nan_nan</t>
-  </si>
-  <si>
-    <t>IL2_pn_nan_nan,IL2_pn_nan_go0005576</t>
-  </si>
-  <si>
-    <t>D,D,D,D</t>
+    <t>NFATC2,NFATC4,NFATC3</t>
+  </si>
+  <si>
+    <t>KRAS,HRAS</t>
+  </si>
+  <si>
+    <t>TSC1,TSC2</t>
+  </si>
+  <si>
+    <t>PIK3CA,PIK3CB,PIK3CG</t>
   </si>
 </sst>
 </file>
@@ -678,7 +744,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,12 +776,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -726,7 +791,10 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1017,7 +1085,7 @@
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="14" max="14" width="112.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="78" customWidth="1"/>
     <col min="18" max="18" width="28.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1025,130 +1093,130 @@
       <c r="A1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AD1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AE1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AG1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AH1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AI1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AK1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AL1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AM1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AN1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AO1" s="5" t="s">
+      <c r="AO1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AP1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1162,20 +1230,26 @@
       <c r="C2" t="s">
         <v>106</v>
       </c>
+      <c r="E2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" t="s">
+        <v>176</v>
+      </c>
       <c r="G2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N2" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="O2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="S2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z2" t="s">
         <v>85</v>
@@ -1216,16 +1290,19 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>194</v>
+      </c>
+      <c r="F3" t="s">
+        <v>176</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z3" t="s">
         <v>86</v>
@@ -1259,24 +1336,32 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="N4" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="R4" s="8"/>
-      <c r="Z4" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="8">
+        <v>29108</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="R4" s="7"/>
+      <c r="Z4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AD4">
@@ -1294,10 +1379,10 @@
       <c r="AH4">
         <v>0</v>
       </c>
-      <c r="AL4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="8" t="s">
+      <c r="AL4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="7" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1311,8 +1396,14 @@
       <c r="C5" t="s">
         <v>106</v>
       </c>
+      <c r="E5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5" t="s">
+        <v>176</v>
+      </c>
       <c r="G5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AB5" t="s">
         <v>36</v>
@@ -1349,8 +1440,14 @@
       <c r="C6" t="s">
         <v>106</v>
       </c>
+      <c r="E6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" t="s">
+        <v>176</v>
+      </c>
       <c r="G6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AB6" t="s">
         <v>37</v>
@@ -1387,14 +1484,20 @@
       <c r="C7" t="s">
         <v>106</v>
       </c>
+      <c r="E7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" t="s">
+        <v>176</v>
+      </c>
       <c r="G7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N7" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="O7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Z7" t="s">
         <v>87</v>
@@ -1434,8 +1537,14 @@
       <c r="C8" t="s">
         <v>106</v>
       </c>
+      <c r="E8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>176</v>
+      </c>
       <c r="G8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AB8" t="s">
         <v>1</v>
@@ -1472,14 +1581,20 @@
       <c r="C9" t="s">
         <v>106</v>
       </c>
+      <c r="E9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F9" t="s">
+        <v>176</v>
+      </c>
       <c r="G9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N9" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z9" t="s">
         <v>9</v>
@@ -1519,14 +1634,20 @@
       <c r="C10" t="s">
         <v>106</v>
       </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>176</v>
+      </c>
       <c r="G10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N10" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="O10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z10" t="s">
         <v>8</v>
@@ -1566,14 +1687,20 @@
       <c r="C11" t="s">
         <v>106</v>
       </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" t="s">
+        <v>176</v>
+      </c>
       <c r="G11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O11" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="Z11" t="s">
         <v>88</v>
@@ -1613,22 +1740,28 @@
       <c r="C12" t="s">
         <v>106</v>
       </c>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>176</v>
+      </c>
       <c r="G12" t="s">
-        <v>119</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>190</v>
+        <v>118</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="S12" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z12" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z12" s="7" t="s">
         <v>89</v>
       </c>
       <c r="AA12" s="2" t="s">
@@ -1669,20 +1802,26 @@
       <c r="C13" t="s">
         <v>106</v>
       </c>
+      <c r="E13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>176</v>
+      </c>
       <c r="G13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H13" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" t="s">
         <v>146</v>
       </c>
-      <c r="I13" t="s">
+      <c r="N13" t="s">
+        <v>175</v>
+      </c>
+      <c r="O13" t="s">
         <v>147</v>
-      </c>
-      <c r="N13" t="s">
-        <v>191</v>
-      </c>
-      <c r="O13" t="s">
-        <v>149</v>
       </c>
       <c r="Z13" t="s">
         <v>90</v>
@@ -1716,20 +1855,25 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" t="s">
-        <v>120</v>
+      <c r="C14" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="N14" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="O14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Z14" t="s">
         <v>91</v>
@@ -1769,14 +1913,20 @@
       <c r="C15" t="s">
         <v>106</v>
       </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>176</v>
+      </c>
       <c r="G15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N15" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="O15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z15" t="s">
         <v>92</v>
@@ -1810,20 +1960,25 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C16" t="s">
-        <v>106</v>
-      </c>
-      <c r="G16" t="s">
-        <v>122</v>
+      <c r="C16" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="N16" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="O16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z16" t="s">
         <v>11</v>
@@ -1863,14 +2018,20 @@
       <c r="C17" t="s">
         <v>106</v>
       </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>176</v>
+      </c>
       <c r="G17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N17" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="O17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z17" t="s">
         <v>12</v>
@@ -1910,14 +2071,20 @@
       <c r="C18" t="s">
         <v>106</v>
       </c>
+      <c r="E18" t="s">
+        <v>185</v>
+      </c>
+      <c r="F18" t="s">
+        <v>176</v>
+      </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N18" t="s">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z18" t="s">
         <v>13</v>
@@ -1957,14 +2124,20 @@
       <c r="C19" t="s">
         <v>106</v>
       </c>
+      <c r="E19" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" t="s">
+        <v>176</v>
+      </c>
       <c r="G19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N19" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="O19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z19" t="s">
         <v>10</v>
@@ -2004,20 +2177,26 @@
       <c r="C20" t="s">
         <v>106</v>
       </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
+        <v>176</v>
+      </c>
       <c r="G20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N20" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="O20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R20" t="s">
+        <v>206</v>
+      </c>
+      <c r="S20" t="s">
         <v>148</v>
-      </c>
-      <c r="S20" t="s">
-        <v>150</v>
       </c>
       <c r="Z20" t="s">
         <v>93</v>
@@ -2051,20 +2230,25 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="G21" t="s">
-        <v>127</v>
+      <c r="C21" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="N21" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="O21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z21" t="s">
         <v>27</v>
@@ -2101,26 +2285,31 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" t="s">
-        <v>128</v>
+      <c r="C22" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="O22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R22" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="S22" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>19</v>
@@ -2157,20 +2346,27 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" t="s">
-        <v>129</v>
+      <c r="C23" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="N23" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="O23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z23" t="s">
         <v>15</v>
@@ -2207,21 +2403,25 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3" t="s">
-        <v>130</v>
+      <c r="C24" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="N24" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Z24" t="s">
         <v>94</v>
@@ -2261,14 +2461,20 @@
       <c r="C25" t="s">
         <v>106</v>
       </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>176</v>
+      </c>
       <c r="G25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N25" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="O25" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z25" t="s">
         <v>20</v>
@@ -2302,27 +2508,34 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G26" t="s">
-        <v>132</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="R26" s="8"/>
-      <c r="Z26" s="8" t="s">
+      <c r="D26" s="8"/>
+      <c r="E26" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="R26" s="7"/>
+      <c r="Z26" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8" t="s">
+      <c r="AA26" s="7"/>
+      <c r="AB26" s="7" t="s">
         <v>19</v>
       </c>
       <c r="AD26">
@@ -2340,10 +2553,10 @@
       <c r="AH26">
         <v>0</v>
       </c>
-      <c r="AL26" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="8" t="s">
+      <c r="AL26" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="7" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2351,35 +2564,38 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>107</v>
       </c>
+      <c r="F27" t="s">
+        <v>178</v>
+      </c>
       <c r="G27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H27" s="2"/>
-      <c r="N27" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="R27" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="S27" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z27" s="8" t="s">
+      <c r="N27" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z27" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="AA27" s="8" t="s">
+      <c r="AA27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="AB27" s="8" t="s">
+      <c r="AB27" s="7" t="s">
         <v>20</v>
       </c>
       <c r="AD27">
@@ -2397,10 +2613,10 @@
       <c r="AH27">
         <v>0</v>
       </c>
-      <c r="AL27" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM27" s="8" t="s">
+      <c r="AL27" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM27" s="7" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2408,20 +2624,27 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="8" t="s">
         <v>106</v>
       </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="G28" s="9" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="N28" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="O28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Z28" t="s">
         <v>96</v>
@@ -2461,14 +2684,20 @@
       <c r="C29" t="s">
         <v>106</v>
       </c>
+      <c r="E29" t="s">
+        <v>188</v>
+      </c>
+      <c r="F29" t="s">
+        <v>176</v>
+      </c>
       <c r="G29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N29" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="O29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z29" t="s">
         <v>29</v>
@@ -2508,20 +2737,26 @@
       <c r="C30" t="s">
         <v>106</v>
       </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" t="s">
+        <v>176</v>
+      </c>
       <c r="G30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Z30" s="3" t="s">
         <v>97</v>
@@ -2550,7 +2785,7 @@
       <c r="AL30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="AM30" s="8" t="s">
+      <c r="AM30" s="7" t="s">
         <v>101</v>
       </c>
       <c r="AN30" t="s">
@@ -2567,14 +2802,20 @@
       <c r="C31" t="s">
         <v>106</v>
       </c>
+      <c r="E31" t="s">
+        <v>189</v>
+      </c>
+      <c r="F31" t="s">
+        <v>176</v>
+      </c>
       <c r="G31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N31" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="O31" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z31" t="s">
         <v>14</v>
@@ -2611,20 +2852,25 @@
       <c r="B32" t="s">
         <v>14</v>
       </c>
-      <c r="C32" t="s">
-        <v>106</v>
+      <c r="C32" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="D32"/>
-      <c r="E32"/>
+      <c r="E32" t="s">
+        <v>212</v>
+      </c>
+      <c r="F32" t="s">
+        <v>176</v>
+      </c>
       <c r="G32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H32"/>
       <c r="N32" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="O32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R32"/>
       <c r="Z32" t="s">
@@ -2667,14 +2913,20 @@
       <c r="C33" t="s">
         <v>106</v>
       </c>
+      <c r="E33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" t="s">
+        <v>176</v>
+      </c>
       <c r="G33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R33" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="S33" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AA33" t="s">
         <v>28</v>
@@ -2714,14 +2966,20 @@
       <c r="C34" t="s">
         <v>106</v>
       </c>
+      <c r="E34" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34" t="s">
+        <v>176</v>
+      </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N34" t="s">
+        <v>206</v>
+      </c>
+      <c r="O34" t="s">
         <v>148</v>
-      </c>
-      <c r="O34" t="s">
-        <v>150</v>
       </c>
       <c r="Z34" t="s">
         <v>24</v>
@@ -2761,14 +3019,20 @@
       <c r="C35" t="s">
         <v>106</v>
       </c>
+      <c r="E35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" t="s">
+        <v>176</v>
+      </c>
       <c r="G35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N35" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="O35" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z35" t="s">
         <v>2</v>
@@ -2808,14 +3072,20 @@
       <c r="C36" t="s">
         <v>106</v>
       </c>
+      <c r="E36" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" t="s">
+        <v>176</v>
+      </c>
       <c r="G36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N36" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="O36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z36" t="s">
         <v>32</v>
@@ -2855,14 +3125,20 @@
       <c r="C37" t="s">
         <v>106</v>
       </c>
+      <c r="E37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F37" t="s">
+        <v>176</v>
+      </c>
       <c r="G37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N37" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="O37" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z37" t="s">
         <v>17</v>
@@ -2896,14 +3172,19 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" t="s">
-        <v>106</v>
-      </c>
-      <c r="G38" t="s">
-        <v>143</v>
+      <c r="B38" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -2945,8 +3226,14 @@
       <c r="C39" t="s">
         <v>106</v>
       </c>
+      <c r="E39" t="s">
+        <v>193</v>
+      </c>
+      <c r="F39" t="s">
+        <v>176</v>
+      </c>
       <c r="G39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AB39" t="s">
         <v>2</v>
@@ -2977,20 +3264,27 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C40" t="s">
-        <v>106</v>
-      </c>
-      <c r="G40" t="s">
-        <v>145</v>
+      <c r="C40" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="R40" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="S40" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AA40" t="s">
         <v>23</v>
@@ -3030,6 +3324,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3038,7 +3338,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A5F0FAD8EF73D449B39728944A2FE003" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="eda1eed5f720a743d7e8e0702734e720">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1cab681b-ff41-4914-9116-6da4adaac831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2c79a46b8f091c582d0b416678c62e2e" ns2:_="">
     <xsd:import namespace="1cab681b-ff41-4914-9116-6da4adaac831"/>
@@ -3176,13 +3476,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179D896-5546-4B0D-A21A-6E2AE9122C3E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88E0DE6F-A777-40E1-A247-169523693BB9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3190,7 +3493,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03D04DA5-A0CE-49F7-B9AE-1669786C8B24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3206,13 +3509,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179D896-5546-4B0D-A21A-6E2AE9122C3E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>